--- a/2022 data/excel_outputs/251_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/251_boothwise_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="454">
   <si>
     <t>Booth No.</t>
   </si>
@@ -1166,6 +1166,216 @@
   </si>
   <si>
     <t>P.S. ASKARANPUR MAGROHANI</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>P.S. ASKARANPUR MAGROHANI ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
   </si>
 </sst>
 </file>
@@ -27303,6 +27513,9 @@
       <c r="A364">
         <v>363</v>
       </c>
+      <c r="B364" t="s">
+        <v>384</v>
+      </c>
       <c r="C364">
         <v>337</v>
       </c>
@@ -27371,6 +27584,9 @@
       <c r="A365">
         <v>364</v>
       </c>
+      <c r="B365" t="s">
+        <v>385</v>
+      </c>
       <c r="C365">
         <v>163</v>
       </c>
@@ -27439,6 +27655,9 @@
       <c r="A366">
         <v>365</v>
       </c>
+      <c r="B366" t="s">
+        <v>386</v>
+      </c>
       <c r="C366">
         <v>212</v>
       </c>
@@ -27507,6 +27726,9 @@
       <c r="A367">
         <v>366</v>
       </c>
+      <c r="B367" t="s">
+        <v>387</v>
+      </c>
       <c r="C367">
         <v>179</v>
       </c>
@@ -27575,6 +27797,9 @@
       <c r="A368">
         <v>367</v>
       </c>
+      <c r="B368" t="s">
+        <v>388</v>
+      </c>
       <c r="C368">
         <v>96</v>
       </c>
@@ -27643,6 +27868,9 @@
       <c r="A369">
         <v>368</v>
       </c>
+      <c r="B369" t="s">
+        <v>389</v>
+      </c>
       <c r="C369">
         <v>251</v>
       </c>
@@ -27711,6 +27939,9 @@
       <c r="A370">
         <v>369</v>
       </c>
+      <c r="B370" t="s">
+        <v>390</v>
+      </c>
       <c r="C370">
         <v>126</v>
       </c>
@@ -27779,6 +28010,9 @@
       <c r="A371">
         <v>370</v>
       </c>
+      <c r="B371" t="s">
+        <v>391</v>
+      </c>
       <c r="C371">
         <v>357</v>
       </c>
@@ -27847,6 +28081,9 @@
       <c r="A372">
         <v>371</v>
       </c>
+      <c r="B372" t="s">
+        <v>392</v>
+      </c>
       <c r="C372">
         <v>231</v>
       </c>
@@ -27915,6 +28152,9 @@
       <c r="A373">
         <v>372</v>
       </c>
+      <c r="B373" t="s">
+        <v>393</v>
+      </c>
       <c r="C373">
         <v>69</v>
       </c>
@@ -27983,6 +28223,9 @@
       <c r="A374">
         <v>373</v>
       </c>
+      <c r="B374" t="s">
+        <v>394</v>
+      </c>
       <c r="C374">
         <v>137</v>
       </c>
@@ -28051,6 +28294,9 @@
       <c r="A375">
         <v>374</v>
       </c>
+      <c r="B375" t="s">
+        <v>395</v>
+      </c>
       <c r="C375">
         <v>340</v>
       </c>
@@ -28119,6 +28365,9 @@
       <c r="A376">
         <v>375</v>
       </c>
+      <c r="B376" t="s">
+        <v>396</v>
+      </c>
       <c r="C376">
         <v>153</v>
       </c>
@@ -28187,6 +28436,9 @@
       <c r="A377">
         <v>376</v>
       </c>
+      <c r="B377" t="s">
+        <v>397</v>
+      </c>
       <c r="C377">
         <v>198</v>
       </c>
@@ -28255,6 +28507,9 @@
       <c r="A378">
         <v>377</v>
       </c>
+      <c r="B378" t="s">
+        <v>398</v>
+      </c>
       <c r="C378">
         <v>141</v>
       </c>
@@ -28323,6 +28578,9 @@
       <c r="A379">
         <v>378</v>
       </c>
+      <c r="B379" t="s">
+        <v>399</v>
+      </c>
       <c r="C379">
         <v>177</v>
       </c>
@@ -28391,6 +28649,9 @@
       <c r="A380">
         <v>379</v>
       </c>
+      <c r="B380" t="s">
+        <v>400</v>
+      </c>
       <c r="C380">
         <v>93</v>
       </c>
@@ -28459,6 +28720,9 @@
       <c r="A381">
         <v>380</v>
       </c>
+      <c r="B381" t="s">
+        <v>401</v>
+      </c>
       <c r="C381">
         <v>145</v>
       </c>
@@ -28527,6 +28791,9 @@
       <c r="A382">
         <v>381</v>
       </c>
+      <c r="B382" t="s">
+        <v>402</v>
+      </c>
       <c r="C382">
         <v>92</v>
       </c>
@@ -28595,6 +28862,9 @@
       <c r="A383">
         <v>382</v>
       </c>
+      <c r="B383" t="s">
+        <v>403</v>
+      </c>
       <c r="C383">
         <v>244</v>
       </c>
@@ -28663,6 +28933,9 @@
       <c r="A384">
         <v>383</v>
       </c>
+      <c r="B384" t="s">
+        <v>404</v>
+      </c>
       <c r="C384">
         <v>68</v>
       </c>
@@ -28731,6 +29004,9 @@
       <c r="A385">
         <v>384</v>
       </c>
+      <c r="B385" t="s">
+        <v>405</v>
+      </c>
       <c r="C385">
         <v>110</v>
       </c>
@@ -28799,6 +29075,9 @@
       <c r="A386">
         <v>385</v>
       </c>
+      <c r="B386" t="s">
+        <v>406</v>
+      </c>
       <c r="C386">
         <v>218</v>
       </c>
@@ -28867,6 +29146,9 @@
       <c r="A387">
         <v>386</v>
       </c>
+      <c r="B387" t="s">
+        <v>407</v>
+      </c>
       <c r="C387">
         <v>111</v>
       </c>
@@ -28935,6 +29217,9 @@
       <c r="A388">
         <v>387</v>
       </c>
+      <c r="B388" t="s">
+        <v>408</v>
+      </c>
       <c r="C388">
         <v>219</v>
       </c>
@@ -29003,6 +29288,9 @@
       <c r="A389">
         <v>388</v>
       </c>
+      <c r="B389" t="s">
+        <v>409</v>
+      </c>
       <c r="C389">
         <v>138</v>
       </c>
@@ -29071,6 +29359,9 @@
       <c r="A390">
         <v>389</v>
       </c>
+      <c r="B390" t="s">
+        <v>410</v>
+      </c>
       <c r="C390">
         <v>82</v>
       </c>
@@ -29139,6 +29430,9 @@
       <c r="A391">
         <v>390</v>
       </c>
+      <c r="B391" t="s">
+        <v>411</v>
+      </c>
       <c r="C391">
         <v>46</v>
       </c>
@@ -29207,6 +29501,9 @@
       <c r="A392">
         <v>391</v>
       </c>
+      <c r="B392" t="s">
+        <v>412</v>
+      </c>
       <c r="C392">
         <v>95</v>
       </c>
@@ -29275,6 +29572,9 @@
       <c r="A393">
         <v>392</v>
       </c>
+      <c r="B393" t="s">
+        <v>413</v>
+      </c>
       <c r="C393">
         <v>81</v>
       </c>
@@ -29343,6 +29643,9 @@
       <c r="A394">
         <v>393</v>
       </c>
+      <c r="B394" t="s">
+        <v>414</v>
+      </c>
       <c r="C394">
         <v>308</v>
       </c>
@@ -29411,6 +29714,9 @@
       <c r="A395">
         <v>394</v>
       </c>
+      <c r="B395" t="s">
+        <v>415</v>
+      </c>
       <c r="C395">
         <v>365</v>
       </c>
@@ -29479,6 +29785,9 @@
       <c r="A396">
         <v>395</v>
       </c>
+      <c r="B396" t="s">
+        <v>416</v>
+      </c>
       <c r="C396">
         <v>84</v>
       </c>
@@ -29547,6 +29856,9 @@
       <c r="A397">
         <v>396</v>
       </c>
+      <c r="B397" t="s">
+        <v>417</v>
+      </c>
       <c r="C397">
         <v>153</v>
       </c>
@@ -29615,6 +29927,9 @@
       <c r="A398">
         <v>397</v>
       </c>
+      <c r="B398" t="s">
+        <v>418</v>
+      </c>
       <c r="C398">
         <v>79</v>
       </c>
@@ -29683,6 +29998,9 @@
       <c r="A399">
         <v>398</v>
       </c>
+      <c r="B399" t="s">
+        <v>419</v>
+      </c>
       <c r="C399">
         <v>252</v>
       </c>
@@ -29751,6 +30069,9 @@
       <c r="A400">
         <v>399</v>
       </c>
+      <c r="B400" t="s">
+        <v>420</v>
+      </c>
       <c r="C400">
         <v>320</v>
       </c>
@@ -29819,6 +30140,9 @@
       <c r="A401">
         <v>400</v>
       </c>
+      <c r="B401" t="s">
+        <v>421</v>
+      </c>
       <c r="C401">
         <v>342</v>
       </c>
@@ -29887,6 +30211,9 @@
       <c r="A402">
         <v>401</v>
       </c>
+      <c r="B402" t="s">
+        <v>422</v>
+      </c>
       <c r="C402">
         <v>121</v>
       </c>
@@ -29955,6 +30282,9 @@
       <c r="A403">
         <v>402</v>
       </c>
+      <c r="B403" t="s">
+        <v>423</v>
+      </c>
       <c r="C403">
         <v>12</v>
       </c>
@@ -30023,6 +30353,9 @@
       <c r="A404">
         <v>403</v>
       </c>
+      <c r="B404" t="s">
+        <v>424</v>
+      </c>
       <c r="C404">
         <v>362</v>
       </c>
@@ -30091,6 +30424,9 @@
       <c r="A405">
         <v>404</v>
       </c>
+      <c r="B405" t="s">
+        <v>425</v>
+      </c>
       <c r="C405">
         <v>143</v>
       </c>
@@ -30159,6 +30495,9 @@
       <c r="A406">
         <v>405</v>
       </c>
+      <c r="B406" t="s">
+        <v>426</v>
+      </c>
       <c r="C406">
         <v>136</v>
       </c>
@@ -30227,6 +30566,9 @@
       <c r="A407">
         <v>406</v>
       </c>
+      <c r="B407" t="s">
+        <v>427</v>
+      </c>
       <c r="C407">
         <v>329</v>
       </c>
@@ -30295,6 +30637,9 @@
       <c r="A408">
         <v>407</v>
       </c>
+      <c r="B408" t="s">
+        <v>428</v>
+      </c>
       <c r="C408">
         <v>166</v>
       </c>
@@ -30363,6 +30708,9 @@
       <c r="A409">
         <v>408</v>
       </c>
+      <c r="B409" t="s">
+        <v>429</v>
+      </c>
       <c r="C409">
         <v>164</v>
       </c>
@@ -30431,6 +30779,9 @@
       <c r="A410">
         <v>409</v>
       </c>
+      <c r="B410" t="s">
+        <v>430</v>
+      </c>
       <c r="C410">
         <v>118</v>
       </c>
@@ -30499,6 +30850,9 @@
       <c r="A411">
         <v>410</v>
       </c>
+      <c r="B411" t="s">
+        <v>431</v>
+      </c>
       <c r="C411">
         <v>297</v>
       </c>
@@ -30567,6 +30921,9 @@
       <c r="A412">
         <v>411</v>
       </c>
+      <c r="B412" t="s">
+        <v>432</v>
+      </c>
       <c r="C412">
         <v>146</v>
       </c>
@@ -30635,6 +30992,9 @@
       <c r="A413">
         <v>412</v>
       </c>
+      <c r="B413" t="s">
+        <v>433</v>
+      </c>
       <c r="C413">
         <v>135</v>
       </c>
@@ -30703,6 +31063,9 @@
       <c r="A414">
         <v>413</v>
       </c>
+      <c r="B414" t="s">
+        <v>434</v>
+      </c>
       <c r="C414">
         <v>319</v>
       </c>
@@ -30771,6 +31134,9 @@
       <c r="A415">
         <v>414</v>
       </c>
+      <c r="B415" t="s">
+        <v>435</v>
+      </c>
       <c r="C415">
         <v>274</v>
       </c>
@@ -30839,6 +31205,9 @@
       <c r="A416">
         <v>415</v>
       </c>
+      <c r="B416" t="s">
+        <v>436</v>
+      </c>
       <c r="C416">
         <v>193</v>
       </c>
@@ -30907,6 +31276,9 @@
       <c r="A417">
         <v>416</v>
       </c>
+      <c r="B417" t="s">
+        <v>437</v>
+      </c>
       <c r="C417">
         <v>0</v>
       </c>
@@ -30975,6 +31347,9 @@
       <c r="A418">
         <v>417</v>
       </c>
+      <c r="B418" t="s">
+        <v>438</v>
+      </c>
       <c r="C418">
         <v>134</v>
       </c>
@@ -31043,6 +31418,9 @@
       <c r="A419">
         <v>418</v>
       </c>
+      <c r="B419" t="s">
+        <v>439</v>
+      </c>
       <c r="C419">
         <v>154</v>
       </c>
@@ -31111,6 +31489,9 @@
       <c r="A420">
         <v>419</v>
       </c>
+      <c r="B420" t="s">
+        <v>440</v>
+      </c>
       <c r="C420">
         <v>338</v>
       </c>
@@ -31179,6 +31560,9 @@
       <c r="A421">
         <v>420</v>
       </c>
+      <c r="B421" t="s">
+        <v>441</v>
+      </c>
       <c r="C421">
         <v>169</v>
       </c>
@@ -31247,6 +31631,9 @@
       <c r="A422">
         <v>421</v>
       </c>
+      <c r="B422" t="s">
+        <v>442</v>
+      </c>
       <c r="C422">
         <v>98</v>
       </c>
@@ -31315,6 +31702,9 @@
       <c r="A423">
         <v>422</v>
       </c>
+      <c r="B423" t="s">
+        <v>443</v>
+      </c>
       <c r="C423">
         <v>308</v>
       </c>
@@ -31383,6 +31773,9 @@
       <c r="A424">
         <v>423</v>
       </c>
+      <c r="B424" t="s">
+        <v>444</v>
+      </c>
       <c r="C424">
         <v>265</v>
       </c>
@@ -31451,6 +31844,9 @@
       <c r="A425">
         <v>424</v>
       </c>
+      <c r="B425" t="s">
+        <v>445</v>
+      </c>
       <c r="C425">
         <v>362</v>
       </c>
@@ -31519,6 +31915,9 @@
       <c r="A426">
         <v>425</v>
       </c>
+      <c r="B426" t="s">
+        <v>446</v>
+      </c>
       <c r="C426">
         <v>356</v>
       </c>
@@ -31587,6 +31986,9 @@
       <c r="A427">
         <v>426</v>
       </c>
+      <c r="B427" t="s">
+        <v>447</v>
+      </c>
       <c r="C427">
         <v>204</v>
       </c>
@@ -31655,6 +32057,9 @@
       <c r="A428">
         <v>427</v>
       </c>
+      <c r="B428" t="s">
+        <v>448</v>
+      </c>
       <c r="C428">
         <v>309</v>
       </c>
@@ -31723,6 +32128,9 @@
       <c r="A429">
         <v>428</v>
       </c>
+      <c r="B429" t="s">
+        <v>449</v>
+      </c>
       <c r="C429">
         <v>136</v>
       </c>
@@ -31791,6 +32199,9 @@
       <c r="A430">
         <v>429</v>
       </c>
+      <c r="B430" t="s">
+        <v>450</v>
+      </c>
       <c r="C430">
         <v>217</v>
       </c>
@@ -31859,6 +32270,9 @@
       <c r="A431">
         <v>430</v>
       </c>
+      <c r="B431" t="s">
+        <v>451</v>
+      </c>
       <c r="C431">
         <v>221</v>
       </c>
@@ -31927,6 +32341,9 @@
       <c r="A432">
         <v>431</v>
       </c>
+      <c r="B432" t="s">
+        <v>452</v>
+      </c>
       <c r="C432">
         <v>218</v>
       </c>
@@ -31994,6 +32411,9 @@
     <row r="433" spans="1:23">
       <c r="A433">
         <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>453</v>
       </c>
       <c r="C433">
         <v>176</v>
